--- a/artfynd/S 3257-2025 artfynd.xlsx
+++ b/artfynd/S 3257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,6 +1238,126 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135180910</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56896</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Harkskärsvägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>625373</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6739095</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3257-2025 artfynd.xlsx
+++ b/artfynd/S 3257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/518502</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118212457</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91459709</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91459688</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,8 +1387,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135180910</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3257-2025 artfynd.xlsx
+++ b/artfynd/S 3257-2025 artfynd.xlsx
@@ -1273,7 +1273,7 @@
         <v>135180910</v>
       </c>
       <c r="B7" t="n">
-        <v>56896</v>
+        <v>56901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 3257-2025 artfynd.xlsx
+++ b/artfynd/S 3257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,6 +1265,131 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91459688</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135180910</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56901</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Harkskärsvägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>625373</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6739095</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135180910</t>
         </is>
       </c>
     </row>
@@ -1275,6 +1400,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
